--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260728.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>17,879,000</t>
+          <t>3,423,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>17,879,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>36,919,540</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>36,919,540</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
